--- a/monitoring_forms/047_home_curfew_monitoring_request_form--monitoring_forms.xlsx
+++ b/monitoring_forms/047_home_curfew_monitoring_request_form--monitoring_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1010,8 +1010,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'location_1'}</t>
+          <t>location_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Location 1'}</t>
+          <t>Location 1</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'location_2'}</t>
+          <t>location_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Location 2'}</t>
+          <t>Location 2</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'location_3'}</t>
+          <t>location_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Location 3'}</t>
+          <t>Location 3</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'location_4'}</t>
+          <t>location_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Location 4'}</t>
+          <t>Location 4</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'in_person'}</t>
+          <t>in_person</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'In Person'}</t>
+          <t>In Person</t>
         </is>
       </c>
     </row>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'asap'}</t>
+          <t>asap</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'ASAP'}</t>
+          <t>ASAP</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1328,12 +1328,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_6}</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 6}</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -1345,12 +1345,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_7}</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 7}</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_8}</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 8}</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_9,_'label':_9}</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 9, 'label': 9}</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -1396,12 +1396,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_10,_'label':_10}</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 10, 'label': 10}</t>
+          <t>10</t>
         </is>
       </c>
     </row>
